--- a/3-sigma-kriterium-PH.xlsx
+++ b/3-sigma-kriterium-PH.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="25601"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51E91267-2785-476B-98F3-3666EC546537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="106" documentId="13_ncr:1_{51E91267-2785-476B-98F3-3666EC546537}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C554FC7B-8EDE-4646-A427-2AD10C87E6BC}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="3sigma" sheetId="4" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>data</t>
   </si>
@@ -69,7 +69,26 @@
     <t>hrubá chyba?</t>
   </si>
   <si>
-    <t>nová data</t>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+      </rPr>
+      <t>←</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> SEM VLOŽIT NOVĚ NAMĚŘENOU HODNOTU</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -79,7 +98,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -116,8 +135,39 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="238"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -126,7 +176,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCFF99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -143,26 +205,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FFFF0000"/>
@@ -178,38 +238,13 @@
         <color rgb="FFFF0000"/>
       </font>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFCCFF99"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -306,7 +341,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="cs-CZ"/>
+          <a:endParaRPr lang="en-US"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -398,7 +433,7 @@
                   <c:v>1.78</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.5</c:v>
+                  <c:v>2.4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -415,7 +450,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'3sigma'!$P$1</c:f>
+              <c:f>'3sigma'!$I$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -438,7 +473,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'3sigma'!$O$2:$O$3</c:f>
+              <c:f>'3sigma'!$H$2:$H$3</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -453,7 +488,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'3sigma'!$P$2:$P$3</c:f>
+              <c:f>'3sigma'!$I$2:$I$3</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="2"/>
@@ -478,7 +513,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'3sigma'!$Q$1</c:f>
+              <c:f>'3sigma'!$J$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -502,7 +537,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'3sigma'!$O$2:$O$3</c:f>
+              <c:f>'3sigma'!$H$2:$H$3</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -517,7 +552,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'3sigma'!$Q$2:$Q$3</c:f>
+              <c:f>'3sigma'!$J$2:$J$3</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="2"/>
@@ -542,7 +577,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>'3sigma'!$R$1</c:f>
+              <c:f>'3sigma'!$K$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -566,7 +601,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'3sigma'!$O$2:$O$3</c:f>
+              <c:f>'3sigma'!$H$2:$H$3</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -581,7 +616,7 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'3sigma'!$R$2:$R$3</c:f>
+              <c:f>'3sigma'!$K$2:$K$3</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="2"/>
@@ -606,7 +641,7 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>'3sigma'!$S$1</c:f>
+              <c:f>'3sigma'!$L$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -629,7 +664,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'3sigma'!$O$2:$O$3</c:f>
+              <c:f>'3sigma'!$H$2:$H$3</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -644,15 +679,15 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'3sigma'!$S$2:$S$3</c:f>
+              <c:f>'3sigma'!$L$2:$L$3</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>1.7914285714285714</c:v>
+                  <c:v>1.784285714285714</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.7914285714285714</c:v>
+                  <c:v>1.784285714285714</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -669,7 +704,7 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>'3sigma'!$T$1</c:f>
+              <c:f>'3sigma'!$M$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -693,7 +728,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'3sigma'!$O$2:$O$3</c:f>
+              <c:f>'3sigma'!$H$2:$H$3</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -708,15 +743,15 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'3sigma'!$T$2:$T$3</c:f>
+              <c:f>'3sigma'!$M$2:$M$3</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>1.0997893337006672</c:v>
+                  <c:v>1.162446895552504</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1.0997893337006672</c:v>
+                  <c:v>1.162446895552504</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -733,7 +768,7 @@
           <c:order val="6"/>
           <c:tx>
             <c:strRef>
-              <c:f>'3sigma'!$U$1</c:f>
+              <c:f>'3sigma'!$N$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -757,7 +792,7 @@
           </c:marker>
           <c:xVal>
             <c:numRef>
-              <c:f>'3sigma'!$O$2:$O$3</c:f>
+              <c:f>'3sigma'!$H$2:$H$3</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
@@ -772,15 +807,15 @@
           </c:xVal>
           <c:yVal>
             <c:numRef>
-              <c:f>'3sigma'!$U$2:$U$3</c:f>
+              <c:f>'3sigma'!$N$2:$N$3</c:f>
               <c:numCache>
                 <c:formatCode>0.000</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>2.4830678091564753</c:v>
+                  <c:v>2.4061245330189243</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2.4830678091564753</c:v>
+                  <c:v>2.4061245330189243</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -807,7 +842,6 @@
         <c:axId val="-1302710064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
-          <c:max val="15"/>
           <c:min val="0"/>
         </c:scaling>
         <c:delete val="0"/>
@@ -960,7 +994,23 @@
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
                   </a:rPr>
-                  <a:t>tloušťka (mm)</a:t>
+                  <a:t>tloušťka fólie (</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="el-GR" sz="1200">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>μ</a:t>
+                </a:r>
+                <a:r>
+                  <a:rPr lang="cs-CZ" sz="1200">
+                    <a:solidFill>
+                      <a:sysClr val="windowText" lastClr="000000"/>
+                    </a:solidFill>
+                  </a:rPr>
+                  <a:t>m)</a:t>
                 </a:r>
               </a:p>
             </c:rich>
@@ -1659,13 +1709,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
+      <xdr:col>14</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
@@ -1699,9 +1749,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Motiv Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1739,9 +1789,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1774,26 +1824,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1826,26 +1859,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2019,56 +2035,42 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U15"/>
+  <dimension ref="A1:O25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" customWidth="1"/>
-    <col min="9" max="9" width="15.7109375" customWidth="1"/>
-    <col min="16" max="21" width="15.7109375" customWidth="1"/>
+    <col min="9" max="14" width="15.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="H1" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="P1" s="5" t="s">
+      <c r="I1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="Q1" s="5" t="s">
+      <c r="J1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="R1" s="5" t="s">
+      <c r="K1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="S1" s="4" t="s">
+      <c r="L1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="T1" s="4" t="s">
+      <c r="M1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="U1" s="4" t="s">
+      <c r="N1" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A2" s="3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
         <v>1.9</v>
       </c>
       <c r="B2">
@@ -2079,53 +2081,40 @@
         <v>4</v>
       </c>
       <c r="F2">
-        <f>COUNT(A2:A100)</f>
-        <v>14</v>
-      </c>
-      <c r="H2" s="3">
-        <v>1.9</v>
-      </c>
-      <c r="I2">
-        <f>IF(ABS(H2-$M$3)&gt;$M$5,1,0)</f>
+        <f>COUNT(A2:A14)</f>
+        <v>13</v>
+      </c>
+      <c r="H2">
         <v>0</v>
       </c>
-      <c r="J2" t="s">
-        <v>4</v>
-      </c>
-      <c r="M2">
-        <f>COUNT(H2:H100)</f>
-        <v>13</v>
-      </c>
-      <c r="O2">
-        <v>0</v>
-      </c>
-      <c r="P2" s="2">
-        <f>AVERAGE(H2:H14)</f>
+      <c r="I2" s="2">
+        <f>AVERAGE(A2:A14)</f>
         <v>1.7369230769230768</v>
       </c>
-      <c r="Q2" s="2">
-        <f>P2-3*STDEVA(H2:H14)</f>
+      <c r="J2" s="2">
+        <f>I2-3*STDEVA(A2:A14)</f>
         <v>1.4012034136507383</v>
       </c>
-      <c r="R2" s="2">
-        <f>P2+3*STDEVA(H2:H14)</f>
+      <c r="K2" s="2">
+        <f>I2+3*STDEVA(A2:A14)</f>
         <v>2.0726427401954153</v>
       </c>
-      <c r="S2" s="2">
+      <c r="L2" s="2">
         <f>AVERAGE(A2:A100)</f>
-        <v>1.7914285714285714</v>
-      </c>
-      <c r="T2" s="2">
-        <f>S2-F5</f>
-        <v>1.0997893337006672</v>
-      </c>
-      <c r="U2" s="2">
-        <f>S2+F5</f>
-        <v>2.4830678091564753</v>
-      </c>
+        <v>1.784285714285714</v>
+      </c>
+      <c r="M2" s="2">
+        <f>L2-3*STDEVA(A2:A100)</f>
+        <v>1.162446895552504</v>
+      </c>
+      <c r="N2" s="2">
+        <f>L2+3*STDEVA(A2:A100)</f>
+        <v>2.4061245330189243</v>
+      </c>
+      <c r="O2" s="2"/>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A3" s="3">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" s="6">
         <v>1.8</v>
       </c>
       <c r="B3">
@@ -2136,55 +2125,41 @@
         <v>2</v>
       </c>
       <c r="F3" s="2">
+        <f>AVERAGE(A2:A14)</f>
+        <v>1.7369230769230768</v>
+      </c>
+      <c r="G3" s="2"/>
+      <c r="H3">
+        <f>COUNT(A2:A100)</f>
+        <v>14</v>
+      </c>
+      <c r="I3" s="2">
+        <f>AVERAGE(A2:A14)</f>
+        <v>1.7369230769230768</v>
+      </c>
+      <c r="J3" s="2">
+        <f>I3-3*STDEVA(A2:A14)</f>
+        <v>1.4012034136507383</v>
+      </c>
+      <c r="K3" s="2">
+        <f>I3+3*STDEVA(A2:A14)</f>
+        <v>2.0726427401954153</v>
+      </c>
+      <c r="L3" s="2">
         <f>AVERAGE(A2:A100)</f>
-        <v>1.7914285714285714</v>
-      </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="3">
-        <v>1.8</v>
-      </c>
-      <c r="I3">
-        <f t="shared" ref="I3:I15" si="1">IF(ABS(H3-$M$3)&gt;$M$5,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="J3" t="s">
-        <v>2</v>
+        <v>1.784285714285714</v>
       </c>
       <c r="M3" s="2">
-        <f>AVERAGE(H2:H100)</f>
-        <v>1.7369230769230768</v>
-      </c>
-      <c r="O3">
-        <f>F2</f>
-        <v>14</v>
-      </c>
-      <c r="P3" s="2">
-        <f>AVERAGE(H2:H14)</f>
-        <v>1.7369230769230768</v>
-      </c>
-      <c r="Q3" s="2">
-        <f>P3-3*STDEVA(H2:H14)</f>
-        <v>1.4012034136507383</v>
-      </c>
-      <c r="R3" s="2">
-        <f>P3+3*STDEVA(H2:H14)</f>
-        <v>2.0726427401954153</v>
-      </c>
-      <c r="S3" s="2">
-        <f>AVERAGE(A2:A100)</f>
-        <v>1.7914285714285714</v>
-      </c>
-      <c r="T3" s="2">
-        <f>S3-F5</f>
-        <v>1.0997893337006672</v>
-      </c>
-      <c r="U3" s="2">
-        <f>S3+F5</f>
-        <v>2.4830678091564753</v>
+        <f>L3-3*STDEVA(A2:A100)</f>
+        <v>1.162446895552504</v>
+      </c>
+      <c r="N3" s="2">
+        <f>L3+3*STDEVA(A2:A100)</f>
+        <v>2.4061245330189243</v>
       </c>
     </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A4" s="3">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="6">
         <v>1.71</v>
       </c>
       <c r="B4">
@@ -2195,27 +2170,13 @@
         <v>1</v>
       </c>
       <c r="F4" s="2">
-        <f>STDEVA(A2:A100)</f>
-        <v>0.23054641257596803</v>
+        <f>STDEVA(A2:A14)</f>
+        <v>0.11190655442411281</v>
       </c>
       <c r="G4" s="2"/>
-      <c r="H4" s="3">
-        <v>1.71</v>
-      </c>
-      <c r="I4">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J4" t="s">
-        <v>1</v>
-      </c>
-      <c r="M4" s="2">
-        <f>STDEVA(H2:H100)</f>
-        <v>0.11190655442411281</v>
-      </c>
     </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A5" s="3">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="6">
         <v>1.7</v>
       </c>
       <c r="B5">
@@ -2227,26 +2188,12 @@
       </c>
       <c r="F5" s="2">
         <f>3*F4</f>
-        <v>0.69163923772790414</v>
+        <v>0.33571966327233843</v>
       </c>
       <c r="G5" s="2"/>
-      <c r="H5" s="3">
-        <v>1.7</v>
-      </c>
-      <c r="I5">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J5" t="s">
-        <v>5</v>
-      </c>
-      <c r="M5" s="2">
-        <f>3*M4</f>
-        <v>0.33571966327233843</v>
-      </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A6" s="3">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" s="6">
         <v>1.74</v>
       </c>
       <c r="B6">
@@ -2254,16 +2201,9 @@
         <v>0</v>
       </c>
       <c r="G6" s="2"/>
-      <c r="H6" s="3">
-        <v>1.74</v>
-      </c>
-      <c r="I6">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A7" s="3">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" s="6">
         <v>1.59</v>
       </c>
       <c r="B7">
@@ -2275,26 +2215,12 @@
       </c>
       <c r="F7" s="2">
         <f>F3-F5</f>
-        <v>1.0997893337006672</v>
+        <v>1.4012034136507383</v>
       </c>
       <c r="G7" s="2"/>
-      <c r="H7" s="3">
-        <v>1.59</v>
-      </c>
-      <c r="I7">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J7" t="s">
-        <v>6</v>
-      </c>
-      <c r="M7" s="2">
-        <f>M3-M5</f>
-        <v>1.4012034136507383</v>
-      </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A8" s="3">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A8" s="6">
         <v>1.78</v>
       </c>
       <c r="B8">
@@ -2306,25 +2232,11 @@
       </c>
       <c r="F8" s="2">
         <f>F3+F5</f>
-        <v>2.4830678091564753</v>
-      </c>
-      <c r="H8" s="3">
-        <v>1.78</v>
-      </c>
-      <c r="I8">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J8" t="s">
-        <v>7</v>
-      </c>
-      <c r="M8" s="2">
-        <f>M3+M5</f>
         <v>2.0726427401954153</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" s="6">
         <v>1.75</v>
       </c>
       <c r="B9">
@@ -2332,16 +2244,9 @@
         <v>0</v>
       </c>
       <c r="G9" s="1"/>
-      <c r="H9" s="3">
-        <v>1.75</v>
-      </c>
-      <c r="I9">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A10" s="3">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A10" s="6">
         <v>1.78</v>
       </c>
       <c r="B10">
@@ -2355,112 +2260,96 @@
         <f>SUM(B2:B100)</f>
         <v>1</v>
       </c>
-      <c r="H10" s="3">
-        <v>1.78</v>
-      </c>
-      <c r="I10">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="M10" s="1">
-        <f>SUM(I2:I100)</f>
-        <v>0</v>
-      </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A11" s="3">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A11" s="6">
         <v>1.9</v>
       </c>
       <c r="B11">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H11" s="3">
-        <v>1.9</v>
-      </c>
-      <c r="I11">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A12" s="3">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
         <v>1.65</v>
       </c>
       <c r="B12">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H12" s="3">
-        <v>1.65</v>
-      </c>
-      <c r="I12">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A13" s="3">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A13" s="6">
         <v>1.5</v>
       </c>
       <c r="B13">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H13" s="3">
-        <v>1.5</v>
-      </c>
-      <c r="I13">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A14" s="3">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A14" s="6">
         <v>1.78</v>
       </c>
       <c r="B14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H14" s="3">
-        <v>1.78</v>
-      </c>
-      <c r="I14">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A15" s="8">
-        <v>2.5</v>
-      </c>
-      <c r="B15" s="7">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A15" s="7">
+        <v>2.4</v>
+      </c>
+      <c r="B15" s="5">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
-      <c r="H15" s="6"/>
+      <c r="C15" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A16" s="7"/>
+      <c r="B16" s="8"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="7"/>
+      <c r="B17" s="8"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="7"/>
+      <c r="B18" s="8"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="7"/>
+      <c r="B19" s="8"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F24" s="2"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F25" s="2"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C15:G15"/>
+  </mergeCells>
   <conditionalFormatting sqref="B2:B15">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M10 G9 F10">
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="lessThan">
+  <conditionalFormatting sqref="G9 F10">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
       <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I15">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
